--- a/backtest_runs/20260410_193731/by_symbol/HRPL/HRPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HRPL/HRPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-6825.270000000002</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98057.84999999999</v>
@@ -725,7 +725,7 @@
         <v>-998.8199999999985</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>97059.03</v>
@@ -817,7 +817,7 @@
         <v>-943.3299999999897</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>96115.70000000001</v>
@@ -863,7 +863,7 @@
         <v>-887.8400000000008</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>95227.86</v>
@@ -909,7 +909,7 @@
         <v>-2330.580000000009</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>92897.28</v>
@@ -1185,7 +1185,7 @@
         <v>-11763.88</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>103051.95</v>
@@ -1231,7 +1231,7 @@
         <v>-3051.950000000004</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100000</v>
@@ -1277,7 +1277,7 @@
         <v>-8323.5</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>91676.5</v>
@@ -1415,7 +1415,7 @@
         <v>-166.4700000000063</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97447.45999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-221.9599999999953</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>97225.5</v>
@@ -1553,7 +1553,7 @@
         <v>-887.8400000000008</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>97835.89</v>
@@ -1645,7 +1645,7 @@
         <v>-443.9199999999905</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>101942.15</v>
